--- a/yuyang_rent_orders_fy_2025-05-01_2026-04-30.xlsx
+++ b/yuyang_rent_orders_fy_2025-05-01_2026-04-30.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB26"/>
+  <dimension ref="A1:BD26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -460,34 +460,36 @@
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="15" customWidth="1" min="25" max="25"/>
     <col width="19" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="6" customWidth="1" min="34" max="34"/>
-    <col width="6" customWidth="1" min="35" max="35"/>
-    <col width="15" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="30" customWidth="1" min="38" max="38"/>
-    <col width="10" customWidth="1" min="39" max="39"/>
-    <col width="12" customWidth="1" min="40" max="40"/>
-    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="6" customWidth="1" min="36" max="36"/>
+    <col width="6" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="30" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
-    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
     <col width="12" customWidth="1" min="44" max="44"/>
     <col width="10" customWidth="1" min="45" max="45"/>
     <col width="12" customWidth="1" min="46" max="46"/>
-    <col width="12" customWidth="1" min="47" max="47"/>
-    <col width="10" customWidth="1" min="48" max="48"/>
-    <col width="18" customWidth="1" min="49" max="49"/>
-    <col width="30" customWidth="1" min="50" max="50"/>
-    <col width="6" customWidth="1" min="51" max="51"/>
-    <col width="10" customWidth="1" min="52" max="52"/>
-    <col width="15" customWidth="1" min="53" max="53"/>
-    <col width="7" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="12" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="18" customWidth="1" min="51" max="51"/>
+    <col width="30" customWidth="1" min="52" max="52"/>
+    <col width="6" customWidth="1" min="53" max="53"/>
+    <col width="10" customWidth="1" min="54" max="54"/>
+    <col width="15" customWidth="1" min="55" max="55"/>
+    <col width="7" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -623,140 +625,150 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>【退款1】退款账号</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>【退款1】退款人</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>超时费合计</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>赔偿合计</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>减免合计</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>隐藏订单</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>应分账金额</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>实分账金额</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>待分账金额</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>业务</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>门店</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>电话</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>顾客openid</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>收款方式</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>支付账号</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>订单号</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>业务日期</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>业务时间</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>结算日期</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>结算时间</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>支付总金额</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>退款总金额</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>订单结余</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>店员姓名</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>店员openid</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>测试</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>临时订单</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>正/闭</t>
         </is>
@@ -850,65 +862,67 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="AA2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>0</v>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
       </c>
       <c r="AC2" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD2" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AH2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>李</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>18179571997</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>oHdTn5VZa5fwlPPaG_rnjVKDLje4</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>支付宝</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>YY_ZL_251115_00001</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="n">
-        <v>45976</v>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>14:09:06</t>
         </is>
       </c>
       <c r="AR2" s="2" t="n">
@@ -916,34 +930,42 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
+          <t>14:09:06</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>14:39:58</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="n">
+      <c r="AV2" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="AU2" s="3" t="n">
+      <c r="AW2" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="AV2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="inlineStr">
         <is>
           <t>崔洋（个人）</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>oHdTn5a0JEbKh7Rm31ilTEXGJ32Y</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>李</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -1047,70 +1069,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>0</v>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
       </c>
       <c r="AC3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AH3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>李雪</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>13693223900</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>oHdTn5UPfcTG9T8ov0CcLB3A3yN8</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
           <t>YY_ZL_251115_00002</t>
-        </is>
-      </c>
-      <c r="AP3" s="2" t="n">
-        <v>45976</v>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>14:25:49</t>
         </is>
       </c>
       <c r="AR3" s="2" t="n">
@@ -1118,34 +1142,42 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
+          <t>14:25:49</t>
+        </is>
+      </c>
+      <c r="AT3" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>15:25:06</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="n">
+      <c r="AV3" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AU3" s="3" t="n">
+      <c r="AW3" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AV3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AX3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>李雪</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -1249,70 +1281,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>0</v>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
       </c>
       <c r="AC4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AH4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>李</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>15652056667</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>oHdTn5c3nN8SE0BsiqF2jN7Plv7Q</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
           <t>YY_ZL_251116_00001</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="n">
-        <v>45977</v>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>09:59:27</t>
         </is>
       </c>
       <c r="AR4" s="2" t="n">
@@ -1320,34 +1354,42 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
+          <t>09:59:27</t>
+        </is>
+      </c>
+      <c r="AT4" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>11:19:11</t>
         </is>
       </c>
-      <c r="AT4" s="3" t="n">
+      <c r="AV4" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AU4" s="3" t="n">
+      <c r="AW4" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AV4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="inlineStr">
+      <c r="AX4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>李</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -1451,70 +1493,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>0</v>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
       </c>
       <c r="AC5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AH5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>商</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>13269606280</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>oHdTn5eEUB1hI1WkIN4xY9r1B710</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
           <t>YY_ZL_251116_00002</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="n">
-        <v>45977</v>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>10:11:47</t>
         </is>
       </c>
       <c r="AR5" s="2" t="n">
@@ -1522,34 +1566,42 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
+          <t>10:11:47</t>
+        </is>
+      </c>
+      <c r="AT5" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>10:39:27</t>
         </is>
       </c>
-      <c r="AT5" s="3" t="n">
+      <c r="AV5" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AU5" s="3" t="n">
+      <c r="AW5" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AV5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="inlineStr">
+      <c r="AX5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>商</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -1653,70 +1705,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>0</v>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
       </c>
       <c r="AC6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AH6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>汪</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>18811225824</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>oHdTn5VOHaGr5IyhiQJt8ziaYzys</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
           <t>YY_ZL_251116_00003</t>
-        </is>
-      </c>
-      <c r="AP6" s="2" t="n">
-        <v>45977</v>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>10:42:59</t>
         </is>
       </c>
       <c r="AR6" s="2" t="n">
@@ -1724,34 +1778,42 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
+          <t>10:42:59</t>
+        </is>
+      </c>
+      <c r="AT6" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>11:33:13</t>
         </is>
       </c>
-      <c r="AT6" s="3" t="n">
+      <c r="AV6" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AU6" s="3" t="n">
+      <c r="AW6" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AV6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="inlineStr">
+      <c r="AX6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>白雪景-工作号</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>汪</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -1855,70 +1917,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>0</v>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
       </c>
       <c r="AC7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AH7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>刘</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>13269083600</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>oHdTn5bdVSTLeJSbp22gflOj_aF8</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
           <t>YY_ZL_251116_00004</t>
-        </is>
-      </c>
-      <c r="AP7" s="2" t="n">
-        <v>45977</v>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>10:51:39</t>
         </is>
       </c>
       <c r="AR7" s="2" t="n">
@@ -1926,34 +1990,42 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
+          <t>10:51:39</t>
+        </is>
+      </c>
+      <c r="AT7" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>11:55:46</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="n">
+      <c r="AV7" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AU7" s="3" t="n">
+      <c r="AW7" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AV7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AX7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>白雪景-工作号</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>刘</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -2057,70 +2129,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>0</v>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
       </c>
       <c r="AC8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AH8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>周</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>13146556880</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>oHdTn5dcQhCOeM9ph7_qp3YPcFIc</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
           <t>YY_ZL_251116_00005</t>
-        </is>
-      </c>
-      <c r="AP8" s="2" t="n">
-        <v>45977</v>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>10:59:41</t>
         </is>
       </c>
       <c r="AR8" s="2" t="n">
@@ -2128,34 +2202,42 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
+          <t>10:59:41</t>
+        </is>
+      </c>
+      <c r="AT8" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>12:12:35</t>
         </is>
       </c>
-      <c r="AT8" s="3" t="n">
+      <c r="AV8" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="AU8" s="3" t="n">
+      <c r="AW8" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="AV8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="inlineStr">
+      <c r="AX8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>白雪景-工作号</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
         </is>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>周</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -2259,70 +2341,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>0</v>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
       </c>
       <c r="AC9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AH9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>何</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>13311513949</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>oHdTn5a0MH46gezpMZFDiXNIGeas</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
           <t>YY_ZL_251116_00006</t>
-        </is>
-      </c>
-      <c r="AP9" s="2" t="n">
-        <v>45977</v>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>11:03:40</t>
         </is>
       </c>
       <c r="AR9" s="2" t="n">
@@ -2330,34 +2414,42 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
+          <t>11:03:40</t>
+        </is>
+      </c>
+      <c r="AT9" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>12:35:36</t>
         </is>
       </c>
-      <c r="AT9" s="3" t="n">
+      <c r="AV9" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="AU9" s="3" t="n">
+      <c r="AW9" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="AV9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AX9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>白雪景-工作号</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>何</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -2418,92 +2510,92 @@
       </c>
       <c r="T10" s="3" t="n"/>
       <c r="Y10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC10" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD10" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AH10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>李源</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>15810602258</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>oHdTn5ULxEoUc3FWTsTxECiJUOzA</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>YY_ZL_251116_00007</t>
         </is>
       </c>
-      <c r="AP10" s="2" t="n">
+      <c r="AR10" s="2" t="n">
         <v>45977</v>
       </c>
-      <c r="AQ10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>11:12:59</t>
         </is>
       </c>
-      <c r="AT10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AV10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AW10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>李源</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -2607,70 +2699,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>0</v>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
       </c>
       <c r="AC11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AH11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>王</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>13311523133</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>oHdTn5al3Db8nx1FdEeoIdPxKzHs</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
           <t>YY_ZL_251116_00008</t>
-        </is>
-      </c>
-      <c r="AP11" s="2" t="n">
-        <v>45977</v>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>11:28:02</t>
         </is>
       </c>
       <c r="AR11" s="2" t="n">
@@ -2678,34 +2772,42 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
+          <t>11:28:02</t>
+        </is>
+      </c>
+      <c r="AT11" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>12:25:43</t>
         </is>
       </c>
-      <c r="AT11" s="3" t="n">
+      <c r="AV11" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AU11" s="3" t="n">
+      <c r="AW11" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AV11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="inlineStr">
+      <c r="AX11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>王</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -2809,70 +2911,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="3" t="n">
-        <v>0</v>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
       </c>
       <c r="AC12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AH12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AK12" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>孙</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>13051427599</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>oHdTn5afH15Ym34v678VK9Yt44Zc</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
           <t>YY_ZL_251116_00009</t>
-        </is>
-      </c>
-      <c r="AP12" s="2" t="n">
-        <v>45977</v>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>12:23:39</t>
         </is>
       </c>
       <c r="AR12" s="2" t="n">
@@ -2880,34 +2984,42 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
+          <t>12:23:39</t>
+        </is>
+      </c>
+      <c r="AT12" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>13:26:43</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="n">
+      <c r="AV12" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AU12" s="3" t="n">
+      <c r="AW12" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AV12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="inlineStr">
+      <c r="AX12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>白雪景-工作号</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
         </is>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>孙</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -3011,70 +3123,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="3" t="n">
-        <v>0</v>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
       </c>
       <c r="AC13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AH13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AK13" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AL13" t="inlineStr">
         <is>
           <t>任</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
+      <c r="AM13" t="inlineStr">
         <is>
           <t>13683215547</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr">
+      <c r="AN13" t="inlineStr">
         <is>
           <t>oHdTn5UXtNYe3rzdtPRxqH2GCUnM</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
           <t>YY_ZL_251116_00011</t>
-        </is>
-      </c>
-      <c r="AP13" s="2" t="n">
-        <v>45977</v>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>12:29:22</t>
         </is>
       </c>
       <c r="AR13" s="2" t="n">
@@ -3082,34 +3196,42 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
+          <t>12:29:22</t>
+        </is>
+      </c>
+      <c r="AT13" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>13:00:16</t>
         </is>
       </c>
-      <c r="AT13" s="3" t="n">
+      <c r="AV13" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="AU13" s="3" t="n">
+      <c r="AW13" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="AV13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="inlineStr">
+      <c r="AX13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>白雪景-工作号</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
         </is>
       </c>
-      <c r="BA13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>任</t>
         </is>
       </c>
-      <c r="BB13" t="inlineStr">
+      <c r="BD13" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -3213,70 +3335,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="n">
-        <v>0</v>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
       </c>
       <c r="AC14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AH14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AK14" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>张</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr">
+      <c r="AM14" t="inlineStr">
         <is>
           <t>18611919611</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
+      <c r="AN14" t="inlineStr">
         <is>
           <t>oHdTn5b11PV5YvRpK4KJN8zg5-Sk</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
           <t>YY_ZL_251116_00012</t>
-        </is>
-      </c>
-      <c r="AP14" s="2" t="n">
-        <v>45977</v>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>12:31:45</t>
         </is>
       </c>
       <c r="AR14" s="2" t="n">
@@ -3284,34 +3408,42 @@
       </c>
       <c r="AS14" t="inlineStr">
         <is>
+          <t>12:31:45</t>
+        </is>
+      </c>
+      <c r="AT14" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>13:05:56</t>
         </is>
       </c>
-      <c r="AT14" s="3" t="n">
+      <c r="AV14" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="AU14" s="3" t="n">
+      <c r="AW14" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="AV14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="inlineStr">
+      <c r="AX14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>白雪景-工作号</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
         </is>
       </c>
-      <c r="BA14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>张</t>
         </is>
       </c>
-      <c r="BB14" t="inlineStr">
+      <c r="BD14" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -3415,70 +3547,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="3" t="n">
-        <v>0</v>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
       </c>
       <c r="AC15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AH15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AK15" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
+      <c r="AL15" t="inlineStr">
         <is>
           <t>周</t>
         </is>
       </c>
-      <c r="AK15" t="inlineStr">
+      <c r="AM15" t="inlineStr">
         <is>
           <t>13146556880</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
+      <c r="AN15" t="inlineStr">
         <is>
           <t>oHdTn5dcQhCOeM9ph7_qp3YPcFIc</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
           <t>YY_ZL_251116_00013</t>
-        </is>
-      </c>
-      <c r="AP15" s="2" t="n">
-        <v>45977</v>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>13:16:10</t>
         </is>
       </c>
       <c r="AR15" s="2" t="n">
@@ -3486,34 +3620,42 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
+          <t>13:16:10</t>
+        </is>
+      </c>
+      <c r="AT15" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>13:50:41</t>
         </is>
       </c>
-      <c r="AT15" s="3" t="n">
+      <c r="AV15" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AU15" s="3" t="n">
+      <c r="AW15" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AV15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="inlineStr">
+      <c r="AX15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>白雪景-工作号</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
         </is>
       </c>
-      <c r="BA15" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>周</t>
         </is>
       </c>
-      <c r="BB15" t="inlineStr">
+      <c r="BD15" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -3617,70 +3759,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="3" t="n">
-        <v>0</v>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
       </c>
       <c r="AC16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="AE16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AH16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AK16" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
+      <c r="AL16" t="inlineStr">
         <is>
           <t>王</t>
         </is>
       </c>
-      <c r="AK16" t="inlineStr">
+      <c r="AM16" t="inlineStr">
         <is>
           <t>18128130707</t>
         </is>
       </c>
-      <c r="AL16" t="inlineStr">
+      <c r="AN16" t="inlineStr">
         <is>
           <t>oHdTn5TF_tWT-yu6-_A1aM87NjT4</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
           <t>YY_ZL_251208_00001</t>
-        </is>
-      </c>
-      <c r="AP16" s="2" t="n">
-        <v>45999</v>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>12:34:44</t>
         </is>
       </c>
       <c r="AR16" s="2" t="n">
@@ -3688,34 +3832,42 @@
       </c>
       <c r="AS16" t="inlineStr">
         <is>
+          <t>12:34:44</t>
+        </is>
+      </c>
+      <c r="AT16" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>13:31:22</t>
         </is>
       </c>
-      <c r="AT16" s="3" t="n">
+      <c r="AV16" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AU16" s="3" t="n">
+      <c r="AW16" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AV16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="inlineStr">
+      <c r="AX16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>白雪景-工作号</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
         </is>
       </c>
-      <c r="BA16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
         <is>
           <t>王</t>
         </is>
       </c>
-      <c r="BB16" t="inlineStr">
+      <c r="BD16" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -3814,100 +3966,110 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="AA17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="3" t="n">
-        <v>0</v>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
       </c>
       <c r="AC17" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD17" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF17" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AH17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AK17" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>国</t>
         </is>
       </c>
-      <c r="AK17" t="inlineStr">
+      <c r="AM17" t="inlineStr">
         <is>
           <t>19800201572</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
+      <c r="AN17" t="inlineStr">
         <is>
           <t>oHdTn5T3tsfqYAjAKtkjlpksksCI</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
+      <c r="AO17" t="inlineStr">
         <is>
           <t>支付宝</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr">
+      <c r="AQ17" t="inlineStr">
         <is>
           <t>YY_ZL_251213_00001</t>
         </is>
       </c>
-      <c r="AP17" s="2" t="n">
+      <c r="AR17" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="AQ17" t="inlineStr">
+      <c r="AS17" t="inlineStr">
         <is>
           <t>17:26:17</t>
         </is>
       </c>
-      <c r="AR17" s="2" t="n">
+      <c r="AT17" s="2" t="n">
         <v>46005</v>
       </c>
-      <c r="AS17" t="inlineStr">
+      <c r="AU17" t="inlineStr">
         <is>
           <t>12:40:47</t>
         </is>
       </c>
-      <c r="AT17" s="3" t="n">
+      <c r="AV17" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="AU17" s="3" t="n">
+      <c r="AW17" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="AV17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="inlineStr">
+      <c r="AX17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="inlineStr">
         <is>
           <t>肖志强（工作号）</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>oHdTn5aIUSizr2uqffZRadZVkrwc</t>
         </is>
       </c>
-      <c r="BA17" t="inlineStr">
+      <c r="BC17" t="inlineStr">
         <is>
           <t>国</t>
         </is>
       </c>
-      <c r="BB17" t="inlineStr">
+      <c r="BD17" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -4006,100 +4168,110 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="AA18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="3" t="n">
-        <v>0</v>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
       </c>
       <c r="AC18" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD18" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF18" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AH18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AK18" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
+      <c r="AL18" t="inlineStr">
         <is>
           <t>刘女士</t>
         </is>
       </c>
-      <c r="AK18" t="inlineStr">
+      <c r="AM18" t="inlineStr">
         <is>
           <t>15210665007</t>
         </is>
       </c>
-      <c r="AL18" t="inlineStr">
+      <c r="AN18" t="inlineStr">
         <is>
           <t>oHdTn5bZmrp8d9uFrYokQg93j_nA</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>支付宝</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr">
+      <c r="AQ18" t="inlineStr">
         <is>
           <t>YY_ZL_251213_00002</t>
         </is>
       </c>
-      <c r="AP18" s="2" t="n">
+      <c r="AR18" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="AQ18" t="inlineStr">
+      <c r="AS18" t="inlineStr">
         <is>
           <t>17:45:16</t>
         </is>
       </c>
-      <c r="AR18" s="2" t="n">
+      <c r="AT18" s="2" t="n">
         <v>46005</v>
       </c>
-      <c r="AS18" t="inlineStr">
+      <c r="AU18" t="inlineStr">
         <is>
           <t>16:40:42</t>
         </is>
       </c>
-      <c r="AT18" s="3" t="n">
+      <c r="AV18" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="AU18" s="3" t="n">
+      <c r="AW18" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="AV18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="inlineStr">
+      <c r="AX18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>肖志强（工作号）</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>oHdTn5aIUSizr2uqffZRadZVkrwc</t>
         </is>
       </c>
-      <c r="BA18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>刘女士</t>
         </is>
       </c>
-      <c r="BB18" t="inlineStr">
+      <c r="BD18" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -4203,70 +4375,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="3" t="n">
-        <v>0</v>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
       </c>
       <c r="AC19" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD19" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF19" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AH19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AK19" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
+      <c r="AL19" t="inlineStr">
         <is>
           <t>途</t>
         </is>
       </c>
-      <c r="AK19" t="inlineStr">
+      <c r="AM19" t="inlineStr">
         <is>
           <t>18810930257</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
+      <c r="AN19" t="inlineStr">
         <is>
           <t>oHdTn5YR-92je5dKQuXXX7T2JoYw</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
           <t>YY_ZL_251220_00001</t>
-        </is>
-      </c>
-      <c r="AP19" s="2" t="n">
-        <v>46011</v>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>17:34:55</t>
         </is>
       </c>
       <c r="AR19" s="2" t="n">
@@ -4274,34 +4448,42 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
+          <t>17:34:55</t>
+        </is>
+      </c>
+      <c r="AT19" s="2" t="n">
+        <v>46011</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>22:01:58</t>
         </is>
       </c>
-      <c r="AT19" s="3" t="n">
+      <c r="AV19" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="AU19" s="3" t="n">
+      <c r="AW19" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="AV19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="inlineStr">
+      <c r="AX19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="inlineStr">
         <is>
           <t>肖志强（工作号）</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>oHdTn5aIUSizr2uqffZRadZVkrwc</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>途</t>
         </is>
       </c>
-      <c r="BB19" t="inlineStr">
+      <c r="BD19" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -4405,70 +4587,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3" t="n">
-        <v>0</v>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
       </c>
       <c r="AC20" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD20" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF20" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AH20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AK20" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
+      <c r="AL20" t="inlineStr">
         <is>
           <t>陈</t>
         </is>
       </c>
-      <c r="AK20" t="inlineStr">
+      <c r="AM20" t="inlineStr">
         <is>
           <t>13825778098</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr">
+      <c r="AN20" t="inlineStr">
         <is>
           <t>oHdTn5ZB5ZSofmEM5Sxzlu_lMYSk</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
           <t>YY_ZL_260110_00001</t>
-        </is>
-      </c>
-      <c r="AP20" s="2" t="n">
-        <v>46032</v>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>13:15:05</t>
         </is>
       </c>
       <c r="AR20" s="2" t="n">
@@ -4476,34 +4660,42 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
+          <t>13:15:05</t>
+        </is>
+      </c>
+      <c r="AT20" s="2" t="n">
+        <v>46032</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>15:39:00</t>
         </is>
       </c>
-      <c r="AT20" s="3" t="n">
+      <c r="AV20" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="AU20" s="3" t="n">
+      <c r="AW20" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="AV20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="inlineStr">
+      <c r="AX20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="inlineStr">
         <is>
           <t>肖志强（工作号）</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>oHdTn5aIUSizr2uqffZRadZVkrwc</t>
         </is>
       </c>
-      <c r="BA20" t="inlineStr">
+      <c r="BC20" t="inlineStr">
         <is>
           <t>陈</t>
         </is>
       </c>
-      <c r="BB20" t="inlineStr">
+      <c r="BD20" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -4607,70 +4799,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="3" t="n">
-        <v>0</v>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
       </c>
       <c r="AC21" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD21" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF21" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AH21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AK21" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
+      <c r="AL21" t="inlineStr">
         <is>
           <t>黄</t>
         </is>
       </c>
-      <c r="AK21" t="inlineStr">
+      <c r="AM21" t="inlineStr">
         <is>
           <t>13267986373</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
+      <c r="AN21" t="inlineStr">
         <is>
           <t>oHdTn5Yji_ybdbCrALf5OSAWSD_4</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
           <t>YY_ZL_260118_00001</t>
-        </is>
-      </c>
-      <c r="AP21" s="2" t="n">
-        <v>46040</v>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>11:10:19</t>
         </is>
       </c>
       <c r="AR21" s="2" t="n">
@@ -4678,34 +4872,42 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
+          <t>11:10:19</t>
+        </is>
+      </c>
+      <c r="AT21" s="2" t="n">
+        <v>46040</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>15:54:23</t>
         </is>
       </c>
-      <c r="AT21" s="3" t="n">
+      <c r="AV21" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="AU21" s="3" t="n">
+      <c r="AW21" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="AV21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="inlineStr">
+      <c r="AX21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="inlineStr">
         <is>
           <t>段春敏</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>oHdTn5Yg9Z-02nOZ2mkavCWAVh8s</t>
         </is>
       </c>
-      <c r="BA21" t="inlineStr">
+      <c r="BC21" t="inlineStr">
         <is>
           <t>黄</t>
         </is>
       </c>
-      <c r="BB21" t="inlineStr">
+      <c r="BD21" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -4809,70 +5011,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="3" t="n">
-        <v>0</v>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
       </c>
       <c r="AC22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="AE22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
+      <c r="AH22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AK22" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
+      <c r="AL22" t="inlineStr">
         <is>
           <t>崔</t>
         </is>
       </c>
-      <c r="AK22" t="inlineStr">
+      <c r="AM22" t="inlineStr">
         <is>
           <t>13810092801</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr">
+      <c r="AN22" t="inlineStr">
         <is>
           <t>oHdTn5U8X2EMkD8uIy6X30ns_gxs</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
           <t>YY_ZL_260124_00001</t>
-        </is>
-      </c>
-      <c r="AP22" s="2" t="n">
-        <v>46046</v>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>12:12:09</t>
         </is>
       </c>
       <c r="AR22" s="2" t="n">
@@ -4880,34 +5084,42 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
+          <t>12:12:09</t>
+        </is>
+      </c>
+      <c r="AT22" s="2" t="n">
+        <v>46046</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>16:53:32</t>
         </is>
       </c>
-      <c r="AT22" s="3" t="n">
+      <c r="AV22" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="AU22" s="3" t="n">
+      <c r="AW22" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="AV22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="inlineStr">
+      <c r="AX22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="inlineStr">
         <is>
           <t>崔洋（个人）</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>oHdTn5a0JEbKh7Rm31ilTEXGJ32Y</t>
         </is>
       </c>
-      <c r="BA22" t="inlineStr">
+      <c r="BC22" t="inlineStr">
         <is>
           <t>崔</t>
         </is>
       </c>
-      <c r="BB22" t="inlineStr">
+      <c r="BD22" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -5011,70 +5223,72 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="3" t="n">
-        <v>0</v>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
       </c>
       <c r="AC23" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD23" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF23" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AH23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AK23" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
+      <c r="AL23" t="inlineStr">
         <is>
           <t>穆彪</t>
         </is>
       </c>
-      <c r="AK23" t="inlineStr">
+      <c r="AM23" t="inlineStr">
         <is>
           <t>18610109067</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
+      <c r="AN23" t="inlineStr">
         <is>
           <t>oHdTn5UZ_V-QjCXfThGWeFN0cF1s</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
           <t>YY_ZL_260124_00002</t>
-        </is>
-      </c>
-      <c r="AP23" s="2" t="n">
-        <v>46046</v>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>13:22:15</t>
         </is>
       </c>
       <c r="AR23" s="2" t="n">
@@ -5082,34 +5296,42 @@
       </c>
       <c r="AS23" t="inlineStr">
         <is>
+          <t>13:22:15</t>
+        </is>
+      </c>
+      <c r="AT23" s="2" t="n">
+        <v>46046</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>16:54:38</t>
         </is>
       </c>
-      <c r="AT23" s="3" t="n">
+      <c r="AV23" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="AU23" s="3" t="n">
+      <c r="AW23" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="AV23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="inlineStr">
+      <c r="AX23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="inlineStr">
         <is>
           <t>崔洋（个人）</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>oHdTn5a0JEbKh7Rm31ilTEXGJ32Y</t>
         </is>
       </c>
-      <c r="BA23" t="inlineStr">
+      <c r="BC23" t="inlineStr">
         <is>
           <t>穆彪</t>
         </is>
       </c>
-      <c r="BB23" t="inlineStr">
+      <c r="BD23" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -5208,65 +5430,67 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="AA24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3" t="n">
-        <v>0</v>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
       </c>
       <c r="AC24" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD24" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF24" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH24" t="inlineStr">
+      <c r="AH24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AK24" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
+      <c r="AL24" t="inlineStr">
         <is>
           <t>尚</t>
         </is>
       </c>
-      <c r="AK24" t="inlineStr">
+      <c r="AM24" t="inlineStr">
         <is>
           <t>17610066373</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
+      <c r="AN24" t="inlineStr">
         <is>
           <t>oHdTn5XUzBo9HNwGGj3IayNA3KSk</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AO24" t="inlineStr">
         <is>
           <t>支付宝</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr">
+      <c r="AQ24" t="inlineStr">
         <is>
           <t>YY_ZL_260125_00001</t>
-        </is>
-      </c>
-      <c r="AP24" s="2" t="n">
-        <v>46047</v>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>13:29:25</t>
         </is>
       </c>
       <c r="AR24" s="2" t="n">
@@ -5274,34 +5498,42 @@
       </c>
       <c r="AS24" t="inlineStr">
         <is>
+          <t>13:29:25</t>
+        </is>
+      </c>
+      <c r="AT24" s="2" t="n">
+        <v>46047</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>16:28:02</t>
         </is>
       </c>
-      <c r="AT24" s="3" t="n">
+      <c r="AV24" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="AU24" s="3" t="n">
+      <c r="AW24" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="AV24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="inlineStr">
+      <c r="AX24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="inlineStr">
         <is>
           <t>肖志强（工作号）</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>oHdTn5aIUSizr2uqffZRadZVkrwc</t>
         </is>
       </c>
-      <c r="BA24" t="inlineStr">
+      <c r="BC24" t="inlineStr">
         <is>
           <t>尚</t>
         </is>
       </c>
-      <c r="BB24" t="inlineStr">
+      <c r="BD24" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -5362,92 +5594,92 @@
       </c>
       <c r="T25" s="3" t="n"/>
       <c r="Y25" s="3" t="n"/>
-      <c r="AA25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC25" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD25" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="AH25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AK25" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="AL25" t="inlineStr">
         <is>
           <t>白雪景 (个人)</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr">
+      <c r="AM25" t="inlineStr">
         <is>
           <t>15810656580</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="AN25" t="inlineStr">
         <is>
           <t>oHdTn5cchichTZYYXEcs5oU8zlRI</t>
         </is>
       </c>
-      <c r="AO25" t="inlineStr">
+      <c r="AQ25" t="inlineStr">
         <is>
           <t>YY_ZL_260310_00001</t>
         </is>
       </c>
-      <c r="AP25" s="2" t="n">
+      <c r="AR25" s="2" t="n">
         <v>46091</v>
       </c>
-      <c r="AQ25" t="inlineStr">
+      <c r="AS25" t="inlineStr">
         <is>
           <t>09:25:23</t>
         </is>
       </c>
-      <c r="AT25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AV25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AW25" t="inlineStr">
+      <c r="AW25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="inlineStr">
         <is>
           <t>白雪景-工作号</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr">
+      <c r="BA25" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA25" t="inlineStr">
+      <c r="BC25" t="inlineStr">
         <is>
           <t>白雪景 (个人)</t>
         </is>
       </c>
-      <c r="BB25" t="inlineStr">
+      <c r="BD25" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -5508,92 +5740,92 @@
       </c>
       <c r="T26" s="3" t="n"/>
       <c r="Y26" s="3" t="n"/>
-      <c r="AA26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC26" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD26" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF26" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AH26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AK26" t="inlineStr">
         <is>
           <t>渔阳</t>
         </is>
       </c>
-      <c r="AJ26" t="inlineStr">
+      <c r="AL26" t="inlineStr">
         <is>
           <t>白雪景 (个人)</t>
         </is>
       </c>
-      <c r="AK26" t="inlineStr">
+      <c r="AM26" t="inlineStr">
         <is>
           <t>15810656580</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr">
+      <c r="AN26" t="inlineStr">
         <is>
           <t>oHdTn5cchichTZYYXEcs5oU8zlRI</t>
         </is>
       </c>
-      <c r="AO26" t="inlineStr">
+      <c r="AQ26" t="inlineStr">
         <is>
           <t>YY_ZL_260310_00002</t>
         </is>
       </c>
-      <c r="AP26" s="2" t="n">
+      <c r="AR26" s="2" t="n">
         <v>46091</v>
       </c>
-      <c r="AQ26" t="inlineStr">
+      <c r="AS26" t="inlineStr">
         <is>
           <t>09:29:58</t>
         </is>
       </c>
-      <c r="AT26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AV26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AW26" t="inlineStr">
+      <c r="AW26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="inlineStr">
         <is>
           <t>白雪景-工作号</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
+      <c r="BA26" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA26" t="inlineStr">
+      <c r="BC26" t="inlineStr">
         <is>
           <t>白雪景 (个人)</t>
         </is>
       </c>
-      <c r="BB26" t="inlineStr">
+      <c r="BD26" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -5610,7 +5842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5627,6 +5859,8 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5700,6 +5934,16 @@
           <t>退款1方式</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>退款1账号</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>退款1退款人</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5758,6 +6002,16 @@
           <t>支付宝</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5820,6 +6074,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5882,6 +6146,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5944,6 +6218,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6006,6 +6290,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6068,6 +6362,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6130,6 +6434,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6192,6 +6506,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6254,6 +6578,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6316,6 +6650,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6378,6 +6722,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6440,6 +6794,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6502,6 +6866,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6564,6 +6938,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6622,6 +7006,16 @@
           <t>支付宝</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6680,6 +7074,16 @@
           <t>支付宝</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6742,6 +7146,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6804,6 +7218,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6866,6 +7290,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6928,6 +7362,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6990,6 +7434,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7046,6 +7500,16 @@
       <c r="N23" t="inlineStr">
         <is>
           <t>支付宝</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7071,6 +7535,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7114,6 +7579,11 @@
           <t>时间</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7150,6 +7620,11 @@
           <t>14:09:34</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7190,6 +7665,11 @@
           <t>14:27:09</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7226,6 +7706,11 @@
           <t>14:39:58</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7266,6 +7751,11 @@
           <t>15:25:06</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7306,6 +7796,11 @@
           <t>10:00:23</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7346,6 +7841,11 @@
           <t>10:12:46</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7386,6 +7886,11 @@
           <t>10:39:27</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7426,6 +7931,11 @@
           <t>10:44:37</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7466,6 +7976,11 @@
           <t>10:53:01</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7506,6 +8021,11 @@
           <t>11:00:22</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7546,6 +8066,11 @@
           <t>11:04:37</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7586,6 +8111,11 @@
           <t>11:19:11</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7626,6 +8156,11 @@
           <t>11:28:43</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7666,6 +8201,11 @@
           <t>11:33:13</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7706,6 +8246,11 @@
           <t>11:55:46</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7746,6 +8291,11 @@
           <t>12:12:35</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7786,6 +8336,11 @@
           <t>12:24:27</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7826,6 +8381,11 @@
           <t>12:25:43</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7866,6 +8426,11 @@
           <t>12:30:15</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7906,6 +8471,11 @@
           <t>12:32:35</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7946,6 +8516,11 @@
           <t>12:35:36</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7986,6 +8561,11 @@
           <t>13:00:16</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8026,6 +8606,11 @@
           <t>13:05:56</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8066,6 +8651,11 @@
           <t>13:16:50</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8106,6 +8696,11 @@
           <t>13:26:43</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8146,6 +8741,11 @@
           <t>13:50:41</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8186,6 +8786,11 @@
           <t>12:37:57</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8226,6 +8831,11 @@
           <t>13:31:22</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8262,6 +8872,11 @@
           <t>17:31:54</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8298,6 +8913,11 @@
           <t>17:46:13</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8334,6 +8954,11 @@
           <t>12:40:47</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8370,6 +8995,11 @@
           <t>16:40:42</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8410,6 +9040,11 @@
           <t>17:37:00</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8450,6 +9085,11 @@
           <t>22:01:58</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8490,6 +9130,11 @@
           <t>13:16:37</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8530,6 +9175,11 @@
           <t>15:39:00</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8570,6 +9220,11 @@
           <t>11:11:26</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8610,6 +9265,11 @@
           <t>15:54:23</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8650,6 +9310,11 @@
           <t>12:13:32</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8690,6 +9355,11 @@
           <t>13:23:12</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8730,6 +9400,11 @@
           <t>16:53:32</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8770,6 +9445,11 @@
           <t>16:54:38</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8806,6 +9486,11 @@
           <t>13:30:39</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8840,6 +9525,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>16:28:02</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>肖志强（工作号）</t>
         </is>
       </c>
     </row>
